--- a/World_Top_100_Companies_R.xlsx
+++ b/World_Top_100_Companies_R.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FRIDAY\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{871687C1-E2EF-4A7D-A857-5663411134FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A2EED27-E7B2-4C01-A10E-B02F73700B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Guide" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="696">
   <si>
     <t>MARKET-CAP ANALYSIS | SECTOR, REGION AND COUNTRY SUMMARIES</t>
   </si>
@@ -2120,6 +2120,9 @@
   </si>
   <si>
     <t xml:space="preserve">DASHBOARD </t>
+  </si>
+  <si>
+    <t>WORLD TOP 100 COMPANIES BY MARKET CAPITALISATION | 31st AUGUST 2026</t>
   </si>
 </sst>
 </file>
@@ -6094,7 +6097,7 @@
   <sheetData>
     <row r="1" spans="1:20" ht="34.950000000000003" customHeight="1">
       <c r="A1" s="32" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
